--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486671_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486671_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7533</v>
+        <v>3.7299</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7022</v>
+        <v>4.6539</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9489</v>
+        <v>-0.924</v>
       </c>
       <c r="G2" t="n">
         <v>3.308</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1419</v>
+        <v>-1.1653</v>
       </c>
       <c r="T2" t="n">
-        <v>0.165</v>
+        <v>0.1167</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3069</v>
+        <v>-1.282</v>
       </c>
       <c r="V2" t="n">
         <v>0.0426</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0326</v>
+        <v>0.8472</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8807</v>
+        <v>3.2967</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8481</v>
+        <v>-2.4495</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.9334</v>
+        <v>0.8732</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4066</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5268</v>
+        <v>1.8243</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5094</v>
+        <v>2.8956</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0768</v>
+        <v>0.9807</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5674</v>
+        <v>1.9148</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4428</v>
+        <v>-2.0223</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4834</v>
+        <v>-1.9318</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0406</v>
+        <v>-0.0905</v>
       </c>
       <c r="P3" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.7377</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.1931</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.9308</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.8421</v>
+        <v>-0.2344</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5644</v>
+        <v>0.7028</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7222</v>
+        <v>-0.9372</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6138</v>
+        <v>-0.3709</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6138</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9328</v>
+        <v>-0.3064</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0347</v>
+        <v>1.5914</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1019</v>
+        <v>-1.8977</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8732</v>
+        <v>-1.9334</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-1.4066</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8243</v>
+        <v>-0.5268</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8956</v>
+        <v>0.5094</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9807</v>
+        <v>1.0768</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9148</v>
+        <v>-0.5674</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0223</v>
+        <v>-2.4428</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9318</v>
+        <v>-2.4834</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0905</v>
+        <v>0.0406</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1488</v>
+        <v>0.5032</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4407</v>
+        <v>1.2751</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5896</v>
+        <v>-0.7719</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3709</v>
+        <v>-0.6138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5795</v>
+        <v>-1.0925</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2895</v>
+        <v>-0.7032</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.29</v>
+        <v>-0.3893</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9447</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>0.717</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0202</v>
+        <v>0.6065</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2098</v>
+        <v>0.1105</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2856</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. LUIS HERRERA</t>
+          <t>J. SECO YANES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.799</v>
+        <v>-1.1891</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2521</v>
+        <v>-1.3349</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.1459</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6027</v>
+        <v>-0.3034</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0619</v>
+        <v>0.386</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6646</v>
+        <v>-0.6895</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.031</v>
+        <v>-0.6481</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6821</v>
+        <v>0.0414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6511</v>
+        <v>-0.6895</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6337</v>
+        <v>0.3447</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6201</v>
+        <v>0.3447</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7723</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5131</v>
+        <v>-0.0208</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7443</v>
+        <v>-0.0071</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2312</v>
+        <v>-0.0137</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1424</v>
+        <v>-0.2856</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1424</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SECO YANES</t>
+          <t>N. LUIS HERRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9533</v>
+        <v>-1.5396</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0247</v>
+        <v>-0.7692</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.7704</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3034</v>
+        <v>0.6027</v>
       </c>
       <c r="H7" t="n">
-        <v>0.386</v>
+        <v>-0.0619</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6895</v>
+        <v>0.6646</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6481</v>
+        <v>-0.031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0414</v>
+        <v>-0.6821</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6895</v>
+        <v>0.6511</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3447</v>
+        <v>0.6337</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3447</v>
+        <v>0.6201</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5792</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>0.215</v>
+        <v>-0.2275</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3032</v>
+        <v>0.2272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0882</v>
+        <v>-0.4547</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2856</v>
+        <v>-1.1424</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5712</v>
+        <v>-1.1424</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1406</v>
+        <v>-1.731</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8962</v>
+        <v>-1.586</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2443</v>
+        <v>-0.145</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6551</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8716</v>
+        <v>-0.462</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3863</v>
+        <v>-0.076</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4854</v>
+        <v>-0.386</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5727</v>
+        <v>-2.0348</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7447</v>
+        <v>-0.331</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8279</v>
+        <v>-1.7038</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0139</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.331</v>
+        <v>0.2068</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.138</v>
+        <v>0.2757</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2277</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. QUINTERO HURTADO</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2023</v>
+        <v>-3.5817</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8868</v>
+        <v>-0.5733</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6845</v>
+        <v>-3.0083</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3843</v>
+        <v>-1.6641</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.166</v>
+        <v>1.6002</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.2183</v>
+        <v>-3.2643</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2794</v>
+        <v>-0.4624</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0273</v>
+        <v>2.9805</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.2521</v>
+        <v>-3.4428</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1048</v>
+        <v>-1.2017</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1387</v>
+        <v>-1.3802</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0338</v>
+        <v>0.1785</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3862</v>
+        <v>2.1239</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2042</v>
+        <v>-1.5861</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5511</v>
+        <v>-0.111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7553</v>
+        <v>-1.4751</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VALDERREY PULIDO</t>
+          <t>J. QUINTERO HURTADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4018</v>
+        <v>-3.8672</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7863</v>
+        <v>-4.5765</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6155</v>
+        <v>0.7093</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4008</v>
+        <v>-4.3843</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7588</v>
+        <v>-0.166</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.642</v>
+        <v>-4.2183</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3037</v>
+        <v>-4.2794</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0346</v>
+        <v>-0.0273</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3383</v>
+        <v>-4.2521</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0972</v>
+        <v>-0.1048</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7934</v>
+        <v>-0.1387</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6962</v>
+        <v>0.0338</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9308</v>
+        <v>0.3862</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0702</v>
+        <v>0.1309</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5518</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5184</v>
+        <v>-0.7305</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>J. VALDERREY PULIDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2007</v>
+        <v>-4.0901</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8696</v>
+        <v>-2.5242</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3312</v>
+        <v>-1.5659</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6641</v>
+        <v>-1.4008</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6002</v>
+        <v>-0.7588</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.2643</v>
+        <v>-0.642</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4624</v>
+        <v>-0.3037</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9805</v>
+        <v>1.0346</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.4428</v>
+        <v>-1.3383</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2017</v>
+        <v>-1.0972</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3802</v>
+        <v>-1.7934</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1785</v>
+        <v>0.6962</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1239</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1239</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2051</v>
+        <v>-0.7585</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4072</v>
+        <v>-0.2898</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7979</v>
+        <v>-0.4687</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.1312</v>
+        <v>-14.8553</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.132299999999999</v>
+        <v>-2.856300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.9988</v>
+        <v>-11.9987</v>
       </c>
       <c r="G13" t="n">
         <v>-8.5158</v>
@@ -1438,19 +1438,19 @@
         <v>-1.0331</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.482800000000001</v>
+        <v>-7.4828</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4709999999999994</v>
+        <v>-0.4709999999999991</v>
       </c>
       <c r="K13" t="n">
-        <v>8.627500000000001</v>
+        <v>8.6275</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.098600000000001</v>
+        <v>-9.098599999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.044600000000001</v>
+        <v>-8.044599999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-9.660500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>10.6194</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.1726</v>
+        <v>-2.8967</v>
       </c>
       <c r="T13" t="n">
-        <v>3.305600000000001</v>
+        <v>3.5815</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.4783</v>
+        <v>-6.4782</v>
       </c>
       <c r="V13" t="n">
         <v>-6.338800000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.437200000000001</v>
+        <v>6.9618</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7898</v>
+        <v>5.9282</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6474</v>
+        <v>1.0336</v>
       </c>
       <c r="G14" t="n">
         <v>4.6598</v>
@@ -1546,13 +1546,13 @@
         <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5924</v>
+        <v>1.117</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9231</v>
+        <v>1.0615</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3307</v>
+        <v>0.0555</v>
       </c>
       <c r="V14" t="n">
         <v>1.1851</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3045</v>
+        <v>2.6651</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2612</v>
+        <v>2.3492</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0433</v>
+        <v>0.3159</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4481</v>
+        <v>0.7518</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8351</v>
+        <v>0.3448</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2832</v>
+        <v>0.407</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7804</v>
+        <v>1.3466</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4759</v>
+        <v>1.6562</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3044</v>
+        <v>-0.3095</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3322</v>
+        <v>-0.5948</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.311</v>
+        <v>-1.3113</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9788</v>
+        <v>0.7165</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4436</v>
+        <v>0.0138</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8404</v>
+        <v>0.4546</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3968</v>
+        <v>-0.4408</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5712</v>
+        <v>1.5133</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5712</v>
+        <v>1.5133</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9137</v>
+        <v>2.0883</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3669</v>
+        <v>2.0201</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0557</v>
+        <v>1.4481</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6963</v>
+        <v>-0.8351</v>
       </c>
       <c r="I16" t="n">
-        <v>1.752</v>
+        <v>2.2832</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9742</v>
+        <v>1.7804</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2011</v>
+        <v>0.4759</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7732</v>
+        <v>1.3044</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0815</v>
+        <v>-0.3322</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8973</v>
+        <v>-1.311</v>
       </c>
       <c r="O16" t="n">
         <v>0.9788</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2675</v>
+        <v>1.2274</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0957</v>
+        <v>1.5993</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1718</v>
+        <v>-0.3719</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>0.5712</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2277</v>
+        <v>0.5712</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4597</v>
+        <v>1.7214</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7286</v>
+        <v>1.1111</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2689</v>
+        <v>0.6103</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7518</v>
+        <v>0.8151</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3448</v>
+        <v>-0.704</v>
       </c>
       <c r="I17" t="n">
-        <v>0.407</v>
+        <v>1.5191</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3466</v>
+        <v>0.1264</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6562</v>
+        <v>0.1242</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3095</v>
+        <v>0.0023</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5948</v>
+        <v>0.6887</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3113</v>
+        <v>-0.8282</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7165</v>
+        <v>1.5169</v>
       </c>
       <c r="P17" t="n">
         <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1916</v>
+        <v>0.2345</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1659</v>
+        <v>0.4135</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0257</v>
+        <v>-0.179</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5133</v>
+        <v>0.5712</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8023</v>
+        <v>1.5497</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.152</v>
+        <v>1.4361</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9543</v>
+        <v>0.1136</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5925</v>
+        <v>1.0557</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.6963</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2615</v>
+        <v>1.752</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0968</v>
+        <v>0.9742</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6688</v>
+        <v>0.2011</v>
       </c>
       <c r="L18" t="n">
-        <v>0.572</v>
+        <v>0.7732</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6893</v>
+        <v>0.0815</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0002</v>
+        <v>-0.8973</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6895</v>
+        <v>0.9788</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0167</v>
+        <v>0.9035</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0552</v>
+        <v>1.1649</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.2615</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5326</v>
+        <v>1.0133</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2837</v>
+        <v>0.1583</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2489</v>
+        <v>0.855</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8151</v>
+        <v>0.5925</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.704</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5191</v>
+        <v>1.2615</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1264</v>
+        <v>-0.0968</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1242</v>
+        <v>-0.6688</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0023</v>
+        <v>0.572</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6887</v>
+        <v>0.6893</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8282</v>
+        <v>-0.0002</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5169</v>
+        <v>0.6895</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9543</v>
+        <v>0.2277</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4139</v>
+        <v>0.2551</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5404</v>
+        <v>-0.0274</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5948</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0433</v>
+        <v>0.0601</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5458</v>
+        <v>0.5347</v>
       </c>
       <c r="G20" t="n">
         <v>1.8525</v>
@@ -2014,13 +2014,13 @@
         <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6783</v>
+        <v>-0.586</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4415</v>
+        <v>-0.338</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2369</v>
+        <v>-0.248</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2856</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. GRADIN</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3934</v>
+        <v>0.4209</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0507</v>
+        <v>0.9391</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6573</v>
+        <v>-0.5182</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.016</v>
+        <v>-2.1861</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2895</v>
+        <v>0.1513</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2735</v>
+        <v>-2.3375</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8563</v>
+        <v>-1.171</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2889</v>
+        <v>1.4625</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5674</v>
+        <v>-2.6336</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8403</v>
+        <v>-1.0151</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.3112</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8409</v>
+        <v>0.2961</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2099</v>
+        <v>-0.1998</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1652</v>
+        <v>0.2686</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0447</v>
+        <v>-0.4685</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5712</v>
+        <v>1.8415</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5712</v>
+        <v>1.8415</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4988</v>
+        <v>-0.0772</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0083</v>
+        <v>-1.2696</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5071</v>
+        <v>1.1924</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1861</v>
+        <v>-0.2564</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1513</v>
+        <v>-1.8208</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3375</v>
+        <v>1.5643</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.171</v>
+        <v>-0.883</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4625</v>
+        <v>-0.9237</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6336</v>
+        <v>0.0407</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0151</v>
+        <v>0.6266</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3112</v>
+        <v>-0.897</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2961</v>
+        <v>1.5236</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9654</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1195</v>
+        <v>0.7585</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6622</v>
+        <v>0.5789</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4574</v>
+        <v>0.1796</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6536</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6832</v>
+        <v>1.3169</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0297</v>
+        <v>-1.4038</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2564</v>
+        <v>-0.2012</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8208</v>
+        <v>1.6276</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5643</v>
+        <v>-1.8288</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.883</v>
+        <v>0.8138</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9237</v>
+        <v>3.0765</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0407</v>
+        <v>-2.2627</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6266</v>
+        <v>-1.0149</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.897</v>
+        <v>-1.4489</v>
       </c>
       <c r="O23" t="n">
-        <v>1.5236</v>
+        <v>0.434</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1821</v>
+        <v>0.593</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1652</v>
+        <v>0.8547</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0169</v>
+        <v>-0.2617</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>S. GRADIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2757</v>
+        <v>-0.3411</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4895</v>
+        <v>-2.0507</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7652</v>
+        <v>1.7096</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2012</v>
+        <v>-0.016</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6276</v>
+        <v>-0.2895</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8288</v>
+        <v>0.2735</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8138</v>
+        <v>-0.8563</v>
       </c>
       <c r="K24" t="n">
-        <v>3.0765</v>
+        <v>-0.2889</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2627</v>
+        <v>-0.5674</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0149</v>
+        <v>0.8403</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4489</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.434</v>
+        <v>0.8409</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R24" t="n">
         <v>0.7723</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5958</v>
+        <v>0.2622</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0273</v>
+        <v>0.1652</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6231</v>
+        <v>0.097</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6138</v>
+        <v>0.5712</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.131</v>
+        <v>16.5101</v>
       </c>
       <c r="E25" t="n">
         <v>11.9988</v>
       </c>
       <c r="F25" t="n">
-        <v>3.132400000000001</v>
+        <v>4.511200000000001</v>
       </c>
       <c r="G25" t="n">
         <v>8.5158</v>
@@ -2374,13 +2374,13 @@
         <v>1.033</v>
       </c>
       <c r="I25" t="n">
-        <v>7.482699999999999</v>
+        <v>7.4827</v>
       </c>
       <c r="J25" t="n">
-        <v>8.0448</v>
+        <v>8.044800000000004</v>
       </c>
       <c r="K25" t="n">
-        <v>9.660699999999999</v>
+        <v>9.6607</v>
       </c>
       <c r="L25" t="n">
         <v>-1.6157</v>
@@ -2404,13 +2404,13 @@
         <v>7.723099999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1727</v>
+        <v>4.5518</v>
       </c>
       <c r="T25" t="n">
-        <v>6.478199999999999</v>
+        <v>6.478300000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.3057</v>
+        <v>-1.9267</v>
       </c>
       <c r="V25" t="n">
         <v>6.338800000000001</v>
